--- a/P02-Finance-Invoice-Intake/Data/Config.xlsx
+++ b/P02-Finance-Invoice-Intake/Data/Config.xlsx
@@ -154,7 +154,13 @@
     <x:t>P01_HospitalDemo</x:t>
   </x:si>
   <x:si>
-    <x:t>Name of the Windows credential with the lab login (the password is not stored here)</x:t>
+    <x:t>LabApiCredential</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P02_LabApi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name of the Windows credential with the lab API login, role finance (the password is not stored here)</x:t>
   </x:si>
   <x:si>
     <x:t>AttachmentFolder</x:t>
@@ -167,6 +173,9 @@
   </x:si>
   <x:si>
     <x:t>ReportFolder</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name of the Windows credential with the Personalportalen login (the password is not stored here)</x:t>
   </x:si>
   <x:si>
     <x:t>Output</x:t>
@@ -699,29 +708,40 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B17" s="0" t="s">
+      <x:c r="C17" s="0" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B18" s="0" t="s">
+      <x:c r="C18" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C18" s="0" t="s">
+    </x:row>
+    <x:row r="19" spans="1:3">
+      <x:c r="A19" s="0" t="s">
         <x:v>52</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>55</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
